--- a/data/sources/countries/suriname.xlsx
+++ b/data/sources/countries/suriname.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE53"/>
+  <dimension ref="A1:BG53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,20 +684,30 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
+          <t>reliability_notes</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>cancelled_motivo</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>source3</t>
         </is>
@@ -731,10 +740,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G2" t="n">
+        <v>740</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -785,6 +792,9 @@
       <c r="R2" t="n">
         <v>2</v>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -810,19 +820,53 @@
           <t>http://www.chungfadaily.com/info.asp?cid=56&amp;id=77175</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
         <v>3</v>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Fuentes confirman que en agosto de 2023 se firmo contrato con el 23rd Metallurgical Construction Group para construir el nuevo edificio del Ministerio de Salud en Paramaribo, financiado por el BID. No se encontro confirmacion explicita del monto especifico de USD 2M para solo el edificio del ministerio.</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>https://www.waterkant.net/suriname/2023/10/13/volksgezondheid-en-bog-krijgen-nieuwbouw/</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>https://gov.sr/nieuw-gebouw-ministerie-volksgezondheid-moet-gezondheidssector-verbeteren-en-versterken/</t>
         </is>
       </c>
+      <c r="BG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -851,10 +895,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G3" t="n">
+        <v>740</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -905,6 +947,9 @@
       <c r="R3" t="n">
         <v>7</v>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -930,20 +975,53 @@
           <t>https://www.23ye.com/xwzx_xq/71.html</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
         <v>3</v>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>Fuentes confirman que el 23rd Metallurgical Construction Group gano la licitacion en 2024 para construir la sede de la Policia de Suriname en Paramaribo, con inicio oficial de obras el 3 de febrero de 2025. No se encontro confirmacion explicita del monto de USD 7M en las fuentes consultadas.</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr">
         <is>
           <t>https://www.surinametimes.com/construction-of-the-police-force-suriname-kps-headquarters-to-start-on-february-3rd/</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>https://www.dbsuriname.com/2024/11/27/nieuw-hoofdbureau-van-politie-komt-maar-niet-van-de-grond/</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>https://www.dbsuriname.com/2025/02/03/na-15-jaar-vandaag-eindelijk-startsein-bouw-hoofdbureau-van-politie/</t>
         </is>
@@ -976,10 +1054,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G4" t="n">
+        <v>740</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1030,6 +1106,9 @@
       <c r="R4" t="n">
         <v>31</v>
       </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1055,20 +1134,53 @@
           <t>https://www.skyscrapercity.com/threads/sme-suriname-road-infrastructure-%E2%80%A2-surinaamse-wegen.1294755/page-2?nested_view=1&amp;sortby=oldest</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -1101,10 +1213,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G5" t="n">
+        <v>740</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1152,6 +1262,10 @@
           <t>PARAMARIBO</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1167,20 +1281,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
         <v>4</v>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Bien documentado: EXIM Bank y Suriname firmaron préstamo concesional de RMB 300M en julio 2012 para la Fase 1 del Proyecto de Vivienda Social (1,000 unidades en Commewijne/Richelieu). El contrato comercial era de USD 70M con China Dalian International (CDIG). AidData registra el proyecto. El asterisco en el monto ('70\*') sugiere estimado parcial, consistente con Fase 1.</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36772/</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>https://www.ibtimes.com/chinas-stake-suriname-why-beijing-interested-small-south-american-country-1286359</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>https://www.waterkant.net/suriname/2012/06/01/china-financiert-bouw-vijfhonderd-huizen-suriname/</t>
         </is>
@@ -1213,10 +1362,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G6" t="n">
+        <v>740</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1267,6 +1414,9 @@
       <c r="R6" t="n">
         <v>30</v>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1282,19 +1432,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
         <v>3</v>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Confirmado: El gobierno chino firmó acuerdo el 2 de enero de 2015 con Suriname para la construcción del Hospital Regional de Wanica (Lelydorp), con donación de RMB 171M (\~USD 27-30M). El 23rd Metallurgical Construction Group (Minmetals) fue el contratista. Construcción iniciada junio 2017, completada febrero 2020. El monto registrado de USD 30M coincide con la donación. AidData y Wikipedia lo confirman.</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36767</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Regional_Hospital_Wanica</t>
         </is>
       </c>
+      <c r="BG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1323,10 +1509,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G7" t="n">
+        <v>740</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1374,6 +1558,10 @@
           <t>PARA</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1399,6 +1587,10 @@
           <t>https://reference-global.com/article/10.2478/ecdip-2024-0002</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. prnewswire.com.</t>
@@ -1409,19 +1601,47 @@
           <t>https://www.prnewswire.com/news-releases/powerchina-successfully-hands-over-first-site-of-the-second-phase-of-suriname-village-microgrid-photovoltaic-project-302162568.html</t>
         </is>
       </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
         <v>3</v>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Confirmado por PR Newswire y GreentechLead. PowerChina firmó contrato fase 1 del proyecto microgrid fotovoltaico en aldeas de Suriname en 2019 (650kW + 2.6MWh almacenamiento). Ubicación en aldeas remotas, no específicamente Brokopondo. Monto de $2M plausible para la fase 1.</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr">
         <is>
           <t>https://www.prnewswire.com/news-releases/powerchina-successfully-hands-over-first-site-of-the-second-phase-of-suriname-village-microgrid-photovoltaic-project-302162568.html</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>https://greentechlead.com/solar/powerchina-constructs-photovoltaic-project-in-suriname-46765</t>
         </is>
       </c>
+      <c r="BG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1450,10 +1670,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G8" t="n">
+        <v>740</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1504,6 +1722,9 @@
       <c r="R8" t="n">
         <v>3600</v>
       </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -1529,6 +1750,10 @@
           <t>https://journal.commodityfrontiers.com/journal-issues/issue-7/zijin-a-growing-metal-mining-chinese-transnational-firm/</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. mccarthy.ca.</t>
@@ -1539,20 +1764,47 @@
           <t>https://www.mccarthy.ca/en/experience/zijin-mining-group-co-acquires-majority-equity-interest-and-all-debts-in-rosebel-gold-mines-n-v-and-also-completed-equipment-buy-out</t>
         </is>
       </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
         <v>5</v>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 3600. Zijin adquirio el 95% de Rosebel Gold Mines a IAMGOLD por USD 360M en efectivo, operacion completada en febrero de 2023.</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>https://www.mining.com/zijin-to-buy-rosebel-from-iamgold-for-360-million/</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>https://www.iamgold.com/English/investors/news-releases/news-releases-details/2022/IAMGOLD-Announces-Agreement-to-Sell-Its-Interest-in-Rosebel-Gold-Mines-to-Zijin-Mining-for-Cash-Consideration-of-360-Million/default.aspx</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>https://www.fasken.com/en/experience/2023/02/iamgold-corporation-completes-sale-of-its-interest-in-rosebel-gold-mines-to-zijin-mining</t>
         </is>
@@ -1585,10 +1837,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G9" t="n">
+        <v>740</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1639,6 +1889,9 @@
       <c r="R9" t="n">
         <v>31</v>
       </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1654,20 +1907,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
         <v>4</v>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -1700,10 +1988,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G10" t="n">
+        <v>740</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1754,6 +2040,9 @@
       <c r="R10" t="n">
         <v>31</v>
       </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1769,20 +2058,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
         <v>4</v>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -1815,10 +2139,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G11" t="n">
+        <v>740</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1869,6 +2191,9 @@
       <c r="R11" t="n">
         <v>31</v>
       </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1884,20 +2209,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
         <v>4</v>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -1930,10 +2290,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G12" t="n">
+        <v>740</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1984,6 +2342,9 @@
       <c r="R12" t="n">
         <v>31</v>
       </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1999,20 +2360,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
         <v>4</v>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -2045,10 +2441,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G13" t="n">
+        <v>740</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2099,6 +2493,9 @@
       <c r="R13" t="n">
         <v>31</v>
       </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2114,20 +2511,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
         <v>4</v>
       </c>
-      <c r="BC13" t="inlineStr">
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD13" t="inlineStr">
+      <c r="BF13" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -2160,10 +2592,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G14" t="n">
+        <v>740</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2214,6 +2644,9 @@
       <c r="R14" t="n">
         <v>31</v>
       </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2229,20 +2662,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="n">
         <v>4</v>
       </c>
-      <c r="BC14" t="inlineStr">
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD14" t="inlineStr">
+      <c r="BF14" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -2275,10 +2743,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G15" t="n">
+        <v>740</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2329,6 +2795,9 @@
       <c r="R15" t="n">
         <v>31</v>
       </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2344,20 +2813,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="n">
         <v>4</v>
       </c>
-      <c r="BC15" t="inlineStr">
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD15" t="inlineStr">
+      <c r="BF15" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -2390,10 +2894,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G16" t="n">
+        <v>740</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2444,6 +2946,9 @@
       <c r="R16" t="n">
         <v>31</v>
       </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2459,20 +2964,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="n">
         <v>4</v>
       </c>
-      <c r="BC16" t="inlineStr">
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD16" t="inlineStr">
+      <c r="BF16" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -2505,10 +3045,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G17" t="n">
+        <v>740</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2559,6 +3097,9 @@
       <c r="R17" t="n">
         <v>31</v>
       </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2574,20 +3115,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="n">
         <v>4</v>
       </c>
-      <c r="BC17" t="inlineStr">
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD17" t="inlineStr">
+      <c r="BF17" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -2620,10 +3196,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G18" t="n">
+        <v>740</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2674,6 +3248,9 @@
       <c r="R18" t="n">
         <v>31</v>
       </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2689,20 +3266,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="n">
         <v>4</v>
       </c>
-      <c r="BC18" t="inlineStr">
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD18" t="inlineStr">
+      <c r="BF18" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -2735,10 +3347,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G19" t="n">
+        <v>740</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2789,6 +3399,9 @@
       <c r="R19" t="n">
         <v>31</v>
       </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2804,20 +3417,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="n">
         <v>4</v>
       </c>
-      <c r="BC19" t="inlineStr">
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD19" t="inlineStr">
+      <c r="BF19" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -2850,10 +3498,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G20" t="n">
+        <v>740</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2904,6 +3550,9 @@
       <c r="R20" t="n">
         <v>31</v>
       </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2919,20 +3568,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="n">
         <v>4</v>
       </c>
-      <c r="BC20" t="inlineStr">
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD20" t="inlineStr">
+      <c r="BF20" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -2965,10 +3649,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G21" t="n">
+        <v>740</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -3019,6 +3701,9 @@
       <c r="R21" t="n">
         <v>31</v>
       </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3034,20 +3719,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="n">
         <v>4</v>
       </c>
-      <c r="BC21" t="inlineStr">
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD21" t="inlineStr">
+      <c r="BF21" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -3080,10 +3800,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G22" t="n">
+        <v>740</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -3134,6 +3852,9 @@
       <c r="R22" t="n">
         <v>31</v>
       </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3149,20 +3870,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
         <v>4</v>
       </c>
-      <c r="BC22" t="inlineStr">
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD22" t="inlineStr">
+      <c r="BF22" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -3195,10 +3951,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G23" t="n">
+        <v>740</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3249,6 +4003,9 @@
       <c r="R23" t="n">
         <v>31</v>
       </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3264,20 +4021,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
         <v>4</v>
       </c>
-      <c r="BC23" t="inlineStr">
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>Bien documentado: China Dalian International firmó contrato de \~USD 215M para rehabilitar 500 km de carreteras en Suriname (incluyendo la ruta Meerzorg-Albina), con inicio de obra en abril 2008. AidData registra la financiación. El monto de USD 31M registrado podría corresponder solo a la sección Meerzorg-Albina, siendo el total del proyecto mucho mayor. IDB también documentó este corredor vial.</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36735/</t>
         </is>
       </c>
-      <c r="BD23" t="inlineStr">
+      <c r="BF23" t="inlineStr">
         <is>
           <t>https://www.roughton.com/projects/rehabilitation-of-meerzorg-albina-highway-suriname</t>
         </is>
       </c>
-      <c r="BE23" t="inlineStr">
+      <c r="BG23" t="inlineStr">
         <is>
           <t>https://www.iadb.org/en/news/suriname-gets-idb-assistance-improve-its-vital-meerzorg-albina-integration-road-corridor</t>
         </is>
@@ -3310,10 +4102,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G24" t="n">
+        <v>740</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3364,6 +4154,9 @@
       <c r="R24" t="n">
         <v>70</v>
       </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3379,19 +4172,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
         <v>3</v>
       </c>
-      <c r="BC24" t="inlineStr">
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>Confirmado: en 2017, China Dalian International Group firmó acuerdo con el Postspaarbank de Suriname para la Fase II del proyecto de vivienda, construyendo 700 unidades (400 en Morgenstond, fase 2). El monto de USD 70M es consistente con las fuentes que reportan el costo del proyecto de vivienda. Suriname Herald y De West documentan el proyecto.</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr">
         <is>
           <t>https://www.srherald.com/suriname/2017/04/01/700-nieuwe-woningen-met-dalian-woningbouwproject/</t>
         </is>
       </c>
-      <c r="BD24" t="inlineStr">
+      <c r="BF24" t="inlineStr">
         <is>
           <t>https://dagbladdewest.com/2018/03/16/dalian-woningbouwproject-fase-ii-krijgt-nutsvoorziening/</t>
         </is>
       </c>
+      <c r="BG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3420,10 +4249,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G25" t="n">
+        <v>740</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -3474,6 +4301,9 @@
       <c r="R25" t="n">
         <v>9</v>
       </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3489,20 +4319,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="n">
         <v>3</v>
       </c>
-      <c r="BC25" t="inlineStr">
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>Fuentes en holandes confirman que CRBC (en JV con Kuldipsingh Infra) construyo el nuevo puente sobre el Canal Saramacca, inaugurado en marzo de 2025. El nombre en la entrada dice Salamaca, probablemente refiriendose al Canal Saramacca; no se confirmo el monto exacto de USD 9M.</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr">
         <is>
           <t>https://www.waterkant.net/suriname/2024/02/04/brug-over-saramacca-doorsteek-enkele-maanden-dicht/</t>
         </is>
       </c>
-      <c r="BD25" t="inlineStr">
+      <c r="BF25" t="inlineStr">
         <is>
           <t>https://gov.sr/nieuwe-brug-over-saramaccakanaal-officieel-geopend/</t>
         </is>
       </c>
-      <c r="BE25" t="inlineStr">
+      <c r="BG25" t="inlineStr">
         <is>
           <t>https://www.itlcs.sr/blijf-op-de-hoogte/afsluiting-brug-over-het-saramaccakanaal-in-het-verlengde-van-t-hogerhuysstraat/</t>
         </is>
@@ -3535,10 +4400,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G26" t="n">
+        <v>740</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3589,6 +4452,9 @@
       <c r="R26" t="n">
         <v>9</v>
       </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3604,20 +4470,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
         <v>3</v>
       </c>
-      <c r="BC26" t="inlineStr">
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>Fuentes en holandes confirman que CRBC (en JV con Kuldipsingh Infra) construyo el nuevo puente sobre el Canal Saramacca, inaugurado en marzo de 2025. El nombre en la entrada dice Salamaca, probablemente refiriendose al Canal Saramacca; no se confirmo el monto exacto de USD 9M.</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr">
         <is>
           <t>https://www.waterkant.net/suriname/2024/02/04/brug-over-saramacca-doorsteek-enkele-maanden-dicht/</t>
         </is>
       </c>
-      <c r="BD26" t="inlineStr">
+      <c r="BF26" t="inlineStr">
         <is>
           <t>https://gov.sr/nieuwe-brug-over-saramaccakanaal-officieel-geopend/</t>
         </is>
       </c>
-      <c r="BE26" t="inlineStr">
+      <c r="BG26" t="inlineStr">
         <is>
           <t>https://www.itlcs.sr/blijf-op-de-hoogte/afsluiting-brug-over-het-saramaccakanaal-in-het-verlengde-van-t-hogerhuysstraat/</t>
         </is>
@@ -3650,10 +4551,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G27" t="n">
+        <v>740</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -3704,6 +4603,9 @@
       <c r="R27" t="n">
         <v>7</v>
       </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3719,20 +4621,61 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
         <v>2</v>
       </c>
-      <c r="BC27" t="inlineStr">
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>Zhen Jiang No. 2 fue seleccionada como contratista para la renovación del ala occidental del Hospital Académico de Paramaribo (AZP). Allison aclara que hay una primera fase en 2018 por USD 8M y una segunda fase posterior sin monto identificable. El registro indica 2023 y USD 7M. Las renovaciones del ala occidental comenzaron en octubre 2023 con duración de 18 meses, financiadas por OPEC. El año registrado (2023) y monto (\~USD 7M) son aproximadamente correctos para la fase más reciente.</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
         <is>
           <t>https://www.waterkant.net/suriname/2019/04/11/video-opening-vernieuwd-beddenhuis-academisch-ziekenhuis-in-suriname/</t>
         </is>
       </c>
-      <c r="BD27" t="inlineStr">
+      <c r="BF27" t="inlineStr">
         <is>
           <t>https://www.allesinsu.com/2018/04/18/ondertekening-overeenkomst-renovatie-beddenhuis-azp/</t>
         </is>
       </c>
-      <c r="BE27" t="inlineStr">
+      <c r="BG27" t="inlineStr">
         <is>
           <t>https://gov.sr/president-woont-opening-nieuwe-azp-afdelingen-bij/</t>
         </is>
@@ -3765,10 +4708,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G28" t="n">
+        <v>740</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -3819,6 +4760,9 @@
       <c r="R28" t="n">
         <v>12</v>
       </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3844,6 +4788,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -3854,14 +4802,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
         <v>0</v>
       </c>
-      <c r="BC28" t="inlineStr">
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3890,10 +4869,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G29" t="n">
+        <v>740</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3944,6 +4921,9 @@
       <c r="R29" t="n">
         <v>12</v>
       </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3969,6 +4949,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -3979,14 +4963,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
         <v>0</v>
       </c>
-      <c r="BC29" t="inlineStr">
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4015,10 +5030,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G30" t="n">
+        <v>740</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4069,6 +5082,9 @@
       <c r="R30" t="n">
         <v>12</v>
       </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4094,6 +5110,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -4104,14 +5124,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
         <v>0</v>
       </c>
-      <c r="BC30" t="inlineStr">
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE30" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4140,10 +5191,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G31" t="n">
+        <v>740</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4194,6 +5243,9 @@
       <c r="R31" t="n">
         <v>12</v>
       </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4219,6 +5271,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -4229,14 +5285,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
         <v>0</v>
       </c>
-      <c r="BC31" t="inlineStr">
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4265,10 +5352,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G32" t="n">
+        <v>740</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4319,6 +5404,9 @@
       <c r="R32" t="n">
         <v>12</v>
       </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4344,6 +5432,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -4354,14 +5446,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
         <v>0</v>
       </c>
-      <c r="BC32" t="inlineStr">
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4390,10 +5513,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G33" t="n">
+        <v>740</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4444,6 +5565,9 @@
       <c r="R33" t="n">
         <v>12</v>
       </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4469,6 +5593,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -4479,14 +5607,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
         <v>0</v>
       </c>
-      <c r="BC33" t="inlineStr">
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4515,10 +5674,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G34" t="n">
+        <v>740</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -4569,6 +5726,9 @@
       <c r="R34" t="n">
         <v>12</v>
       </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4594,6 +5754,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -4604,14 +5768,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
         <v>0</v>
       </c>
-      <c r="BC34" t="inlineStr">
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE34" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4640,10 +5835,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G35" t="n">
+        <v>740</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -4694,6 +5887,9 @@
       <c r="R35" t="n">
         <v>12</v>
       </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4719,6 +5915,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -4729,14 +5929,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
         <v>0</v>
       </c>
-      <c r="BC35" t="inlineStr">
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4765,10 +5996,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G36" t="n">
+        <v>740</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -4819,6 +6048,9 @@
       <c r="R36" t="n">
         <v>12</v>
       </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4844,6 +6076,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -4854,14 +6090,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
         <v>0</v>
       </c>
-      <c r="BC36" t="inlineStr">
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4890,10 +6157,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G37" t="n">
+        <v>740</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -4944,6 +6209,9 @@
       <c r="R37" t="n">
         <v>12</v>
       </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4969,6 +6237,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -4979,14 +6251,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
         <v>0</v>
       </c>
-      <c r="BC37" t="inlineStr">
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5015,10 +6318,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G38" t="n">
+        <v>740</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -5069,6 +6370,9 @@
       <c r="R38" t="n">
         <v>12</v>
       </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5094,6 +6398,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -5104,14 +6412,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
         <v>0</v>
       </c>
-      <c r="BC38" t="inlineStr">
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5140,10 +6479,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G39" t="n">
+        <v>740</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -5194,6 +6531,9 @@
       <c r="R39" t="n">
         <v>12</v>
       </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5219,6 +6559,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -5229,14 +6573,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
         <v>0</v>
       </c>
-      <c r="BC39" t="inlineStr">
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5265,10 +6640,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G40" t="n">
+        <v>740</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -5319,6 +6692,9 @@
       <c r="R40" t="n">
         <v>12</v>
       </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5344,6 +6720,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -5354,14 +6734,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
         <v>0</v>
       </c>
-      <c r="BC40" t="inlineStr">
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE40" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5390,10 +6801,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G41" t="n">
+        <v>740</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -5444,6 +6853,9 @@
       <c r="R41" t="n">
         <v>12</v>
       </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5469,6 +6881,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -5479,14 +6895,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
         <v>0</v>
       </c>
-      <c r="BC41" t="inlineStr">
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5515,10 +6962,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G42" t="n">
+        <v>740</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -5569,6 +7014,9 @@
       <c r="R42" t="n">
         <v>12</v>
       </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5594,6 +7042,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -5604,14 +7056,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
         <v>0</v>
       </c>
-      <c r="BC42" t="inlineStr">
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE42" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5640,10 +7123,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G43" t="n">
+        <v>740</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -5694,6 +7175,9 @@
       <c r="R43" t="n">
         <v>12</v>
       </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5719,6 +7203,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -5729,14 +7217,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
         <v>0</v>
       </c>
-      <c r="BC43" t="inlineStr">
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5765,10 +7284,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G44" t="n">
+        <v>740</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5819,6 +7336,9 @@
       <c r="R44" t="n">
         <v>12</v>
       </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5844,6 +7364,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -5854,14 +7378,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
         <v>0</v>
       </c>
-      <c r="BC44" t="inlineStr">
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE44" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5890,10 +7445,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G45" t="n">
+        <v>740</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5944,6 +7497,9 @@
       <c r="R45" t="n">
         <v>12</v>
       </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5969,6 +7525,10 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. iho.int.</t>
@@ -5979,14 +7539,45 @@
           <t>https://iho.int/uploads/user/Inter-Regional%20Coordination/RHC/MACHC/MACHC22/MACHC22_2021_03.11_EN_National.Report_Suriname_v1.pdf</t>
         </is>
       </c>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
         <v>0</v>
       </c>
-      <c r="BC45" t="inlineStr">
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
         <is>
           <t>https://www.dutchdredging.nl/en/projects/maintenance-dredging/suriname-river-dredging-project-2021</t>
         </is>
       </c>
+      <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6015,10 +7606,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G46" t="n">
+        <v>740</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -6069,6 +7658,9 @@
       <c r="R46" t="n">
         <v>11.2</v>
       </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -6094,6 +7686,10 @@
           <t>https://www.frstrategie.org/sites/default/files/documents/publications/recherches-et-documents/2023/132023.pdf</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. mingjinjituan.com.</t>
@@ -6104,14 +7700,49 @@
           <t>http://www.mingjinjituan.com/page/html/company.php</t>
         </is>
       </c>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="n">
         <v>1</v>
       </c>
-      <c r="BC46" t="inlineStr">
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>Allison no pudo encontrar nada (ni monto ni inversión). La única fuente es un documento de investigación francés (FRS). La búsqueda web no arroja resultados para China Mingjin Group y Sara Kreek gold mine. Sara Kreek es un proyecto minero conocido en Suriname (asociado a Canarc Resource Corp), pero no hay evidencia pública de adquisición por China Mingjin Group.</t>
+        </is>
+      </c>
+      <c r="BC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE46" t="inlineStr">
         <is>
           <t>https://www.frstrategie.org/sites/default/files/documents/publications/recherches-et-documents/2023/132023.pdf</t>
         </is>
       </c>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6119,6 +7750,7 @@
           <t>SUR-0016</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>16</v>
       </c>
@@ -6137,10 +7769,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G47" t="n">
+        <v>740</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -6191,6 +7821,9 @@
       <c r="R47" t="n">
         <v>11.2</v>
       </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6206,22 +7839,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="n">
         <v>3</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="n">
         <v>0</v>
       </c>
-      <c r="BC47" t="inlineStr">
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr">
         <is>
           <t>https://thedailycpec.com/china-suriname-deepen-27-year-cooperation/</t>
         </is>
       </c>
-      <c r="BD47" t="inlineStr">
+      <c r="BF47" t="inlineStr">
         <is>
           <t>https://sr.china-embassy.gov.cn/eng/sbgxyw/202511/t20251106_11747900.htm</t>
         </is>
       </c>
+      <c r="BG47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6229,6 +7893,7 @@
           <t>SUR-0016</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>16</v>
       </c>
@@ -6247,10 +7912,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G48" t="n">
+        <v>740</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -6301,6 +7964,9 @@
       <c r="R48" t="n">
         <v>11.2</v>
       </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6316,22 +7982,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
       <c r="BA48" t="n">
         <v>3</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="n">
         <v>0</v>
       </c>
-      <c r="BC48" t="inlineStr">
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr">
         <is>
           <t>https://thedailycpec.com/china-suriname-deepen-27-year-cooperation/</t>
         </is>
       </c>
-      <c r="BD48" t="inlineStr">
+      <c r="BF48" t="inlineStr">
         <is>
           <t>https://sr.china-embassy.gov.cn/eng/sbgxyw/202511/t20251106_11747900.htm</t>
         </is>
       </c>
+      <c r="BG48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6339,6 +8036,7 @@
           <t>SUR-0016</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>16</v>
       </c>
@@ -6357,10 +8055,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G49" t="n">
+        <v>740</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -6411,6 +8107,9 @@
       <c r="R49" t="n">
         <v>11.2</v>
       </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6426,22 +8125,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
         <v>3</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="n">
         <v>0</v>
       </c>
-      <c r="BC49" t="inlineStr">
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr">
         <is>
           <t>https://thedailycpec.com/china-suriname-deepen-27-year-cooperation/</t>
         </is>
       </c>
-      <c r="BD49" t="inlineStr">
+      <c r="BF49" t="inlineStr">
         <is>
           <t>https://sr.china-embassy.gov.cn/eng/sbgxyw/202511/t20251106_11747900.htm</t>
         </is>
       </c>
+      <c r="BG49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6449,6 +8179,7 @@
           <t>SUR-0016</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>16</v>
       </c>
@@ -6467,10 +8198,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G50" t="n">
+        <v>740</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -6521,6 +8250,9 @@
       <c r="R50" t="n">
         <v>11.2</v>
       </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6536,22 +8268,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
         <v>3</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="n">
         <v>0</v>
       </c>
-      <c r="BC50" t="inlineStr">
+      <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr">
         <is>
           <t>https://thedailycpec.com/china-suriname-deepen-27-year-cooperation/</t>
         </is>
       </c>
-      <c r="BD50" t="inlineStr">
+      <c r="BF50" t="inlineStr">
         <is>
           <t>https://sr.china-embassy.gov.cn/eng/sbgxyw/202511/t20251106_11747900.htm</t>
         </is>
       </c>
+      <c r="BG50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6559,6 +8322,7 @@
           <t>SUR-0016</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>16</v>
       </c>
@@ -6577,10 +8341,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G51" t="n">
+        <v>740</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -6631,6 +8393,9 @@
       <c r="R51" t="n">
         <v>11.2</v>
       </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6646,22 +8411,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
         <v>3</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="n">
         <v>0</v>
       </c>
-      <c r="BC51" t="inlineStr">
+      <c r="BD51" t="inlineStr"/>
+      <c r="BE51" t="inlineStr">
         <is>
           <t>https://thedailycpec.com/china-suriname-deepen-27-year-cooperation/</t>
         </is>
       </c>
-      <c r="BD51" t="inlineStr">
+      <c r="BF51" t="inlineStr">
         <is>
           <t>https://sr.china-embassy.gov.cn/eng/sbgxyw/202511/t20251106_11747900.htm</t>
         </is>
       </c>
+      <c r="BG51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6669,6 +8465,7 @@
           <t>SUR-0016</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>16</v>
       </c>
@@ -6687,10 +8484,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G52" t="n">
+        <v>740</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -6741,6 +8536,9 @@
       <c r="R52" t="n">
         <v>11.2</v>
       </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6756,22 +8554,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
         <v>3</v>
       </c>
-      <c r="BB52" t="n">
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="n">
         <v>0</v>
       </c>
-      <c r="BC52" t="inlineStr">
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr">
         <is>
           <t>https://thedailycpec.com/china-suriname-deepen-27-year-cooperation/</t>
         </is>
       </c>
-      <c r="BD52" t="inlineStr">
+      <c r="BF52" t="inlineStr">
         <is>
           <t>https://sr.china-embassy.gov.cn/eng/sbgxyw/202511/t20251106_11747900.htm</t>
         </is>
       </c>
+      <c r="BG52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6779,6 +8608,7 @@
           <t>SUR-0016</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>16</v>
       </c>
@@ -6797,10 +8627,8 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
+      <c r="G53" t="n">
+        <v>740</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -6851,6 +8679,9 @@
       <c r="R53" t="n">
         <v>11.2</v>
       </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6866,22 +8697,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
         <v>3</v>
       </c>
-      <c r="BB53" t="n">
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="n">
         <v>0</v>
       </c>
-      <c r="BC53" t="inlineStr">
+      <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr">
         <is>
           <t>https://thedailycpec.com/china-suriname-deepen-27-year-cooperation/</t>
         </is>
       </c>
-      <c r="BD53" t="inlineStr">
+      <c r="BF53" t="inlineStr">
         <is>
           <t>https://sr.china-embassy.gov.cn/eng/sbgxyw/202511/t20251106_11747900.htm</t>
         </is>
       </c>
+      <c r="BG53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
